--- a/output/pdf_financials_xlsx/RAY.xlsx
+++ b/output/pdf_financials_xlsx/RAY.xlsx
@@ -431,6 +431,19 @@
   </sheetPr>
   <dimension ref="A1:K135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/RAY.xlsx
+++ b/output/pdf_financials_xlsx/RAY.xlsx
@@ -4079,16 +4079,16 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>12.882</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>18.225</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>23.43</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>40.302</v>
@@ -4547,10 +4547,10 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.819</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="113">
@@ -10532,7 +10532,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -12680,7 +12684,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -14948,7 +14956,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -16928,7 +16936,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">

--- a/output/pdf_financials_xlsx/RAY.xlsx
+++ b/output/pdf_financials_xlsx/RAY.xlsx
@@ -1871,28 +1871,28 @@
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>1.929</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>3.858</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>3.915</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>7.355</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>6.464</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>4.924</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>5.123</v>
       </c>
     </row>
     <row r="41">
@@ -1908,28 +1908,28 @@
         <v>27.073</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>35.444</v>
+        <v>37.373</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>68.861</v>
+        <v>72.71899999999999</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>73.456</v>
+        <v>77.371</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>61.114</v>
+        <v>68.46899999999999</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>66.666</v>
+        <v>73.13</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>71.251</v>
+        <v>76.175</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>72.002</v>
+        <v>75.05200000000001</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>82.574</v>
+        <v>87.697</v>
       </c>
     </row>
     <row r="42">
@@ -2188,7 +2188,7 @@
         <v>17.374</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>14.37</v>
+        <v>9.247</v>
       </c>
     </row>
     <row r="49">
@@ -2890,28 +2890,28 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>26.297</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>46.748</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>40.101</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>34.172</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>32.651</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>36.98</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>36.962</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>35.039</v>
       </c>
     </row>
     <row r="68">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-1.665</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="F114" s="3" t="n">
         <v>0</v>
@@ -4615,16 +4615,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-0.703</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-0.158</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-0.169</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-0.021</v>
       </c>
     </row>
     <row r="115">
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-1.129</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.598</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -10342,7 +10342,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -12276,7 +12280,11 @@
           <t>Acquisition of investments 17</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -16480,7 +16488,11 @@
           <t>Acquisition of an investment 16</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -20080,7 +20092,11 @@
           <t>Acquisition of investments 15</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E232" s="5" t="n">
         <v>-1.665</v>
       </c>
@@ -20146,7 +20162,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E233" s="5" t="n">
         <v>-1.129</v>
       </c>
@@ -24658,7 +24678,11 @@
           <t>Income tax recovery 10</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -25828,7 +25852,11 @@
           <t>Income tax recovery 7</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -26732,7 +26760,11 @@
           <t>Income taxes (recovery) 7</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E338" s="5" t="n">
         <v>0.275</v>
       </c>
